--- a/stock_scan/output/scan_2026-07-16.xlsx
+++ b/stock_scan/output/scan_2026-07-16.xlsx
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,10 +62,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,7 +439,7 @@
     <col width="9.600000000000001" customWidth="1" min="2" max="2"/>
     <col width="12.8" customWidth="1" min="3" max="3"/>
     <col width="14.4" customWidth="1" min="4" max="4"/>
-    <col width="38.40000000000001" customWidth="1" min="5" max="5"/>
+    <col width="35.2" customWidth="1" min="5" max="5"/>
     <col width="11.2" customWidth="1" min="6" max="6"/>
     <col width="9.600000000000001" customWidth="1" min="7" max="7"/>
     <col width="12.8" customWidth="1" min="8" max="8"/>
@@ -522,23 +528,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>156.56</v>
+        <v>151.8</v>
       </c>
       <c r="E2" t="n">
-        <v>1.900546732621722</v>
+        <v>-1.197604790419149</v>
       </c>
       <c r="F2" t="n">
-        <v>2.89</v>
+        <v>4.21</v>
       </c>
       <c r="G2" t="n">
-        <v>1.02</v>
+        <v>0.75</v>
       </c>
       <c r="H2" t="n">
-        <v>-9.5</v>
+        <v>-12.25</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -574,19 +580,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>332.5</v>
+        <v>320.4</v>
       </c>
       <c r="E3" t="n">
-        <v>2.588627317885894</v>
+        <v>-1.144673104810101</v>
       </c>
       <c r="F3" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="H3" t="n">
-        <v>-8.52</v>
+        <v>-11.85</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -626,19 +632,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>112.79</v>
+        <v>109.85</v>
       </c>
       <c r="E4" t="n">
-        <v>1.502879769618426</v>
+        <v>-1.142908567314627</v>
       </c>
       <c r="F4" t="n">
-        <v>2.45</v>
+        <v>3.77</v>
       </c>
       <c r="G4" t="n">
-        <v>1.26</v>
+        <v>0.98</v>
       </c>
       <c r="H4" t="n">
-        <v>5.27</v>
+        <v>2.53</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -678,19 +684,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>531.75</v>
+        <v>514.61</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.002570873922243</v>
+        <v>-10.00017488938246</v>
       </c>
       <c r="F5" t="n">
-        <v>5.02</v>
+        <v>8.16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-19.86</v>
+        <v>-22.44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -730,19 +736,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>227.59</v>
+        <v>211.13</v>
       </c>
       <c r="E6" t="n">
-        <v>-9.929555168592685</v>
+        <v>-16.44372328637012</v>
       </c>
       <c r="F6" t="n">
-        <v>4.31</v>
+        <v>10.13</v>
       </c>
       <c r="G6" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="H6" t="n">
-        <v>-20.37</v>
+        <v>-26.13</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -759,9 +765,9 @@
           <t>否</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>黄色加速</t>
         </is>
       </c>
     </row>
@@ -782,19 +788,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1327.73</v>
+        <v>1279.22</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.464236415181153</v>
+        <v>-5.064343282917494</v>
       </c>
       <c r="F7" t="n">
-        <v>1.06</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="H7" t="n">
-        <v>-13.5</v>
+        <v>-16.66</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -803,7 +809,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -834,19 +840,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>339.88</v>
+        <v>327.85</v>
       </c>
       <c r="E8" t="n">
-        <v>2.552652223764396</v>
+        <v>-1.077183030595619</v>
       </c>
       <c r="F8" t="n">
-        <v>4.13</v>
+        <v>5.94</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21</v>
+        <v>0.88</v>
       </c>
       <c r="H8" t="n">
-        <v>-15.14</v>
+        <v>-18.14</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -886,19 +892,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>72.59999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4983388704318914</v>
+        <v>-2.879291251384275</v>
       </c>
       <c r="F9" t="n">
-        <v>3.55</v>
+        <v>5.84</v>
       </c>
       <c r="G9" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="H9" t="n">
-        <v>-16.64</v>
+        <v>-19.44</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -938,19 +944,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>251.5</v>
+        <v>243.56</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5850264843070607</v>
+        <v>-3.723614514981421</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9</v>
+        <v>3.06</v>
       </c>
       <c r="G10" t="n">
-        <v>0.84</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-23.45</v>
+        <v>-25.87</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -990,19 +996,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>720.33</v>
+        <v>702.76</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.006759486171318</v>
+        <v>-5.372579646136854</v>
       </c>
       <c r="F11" t="n">
-        <v>0.97</v>
+        <v>1.86</v>
       </c>
       <c r="G11" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="H11" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1042,19 +1048,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>374.87</v>
+        <v>361.42</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.196376089345499</v>
+        <v>-7.633724347670523</v>
       </c>
       <c r="F12" t="n">
-        <v>1.74</v>
+        <v>3.38</v>
       </c>
       <c r="G12" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-20.51</v>
+        <v>-23.36</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1094,19 +1100,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>739.05</v>
+        <v>722</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.515503875968996</v>
+        <v>-6.718346253229979</v>
       </c>
       <c r="F13" t="n">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="G13" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="H13" t="n">
-        <v>-10.2</v>
+        <v>-12.27</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1146,19 +1152,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>360.49</v>
+        <v>349</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.317599098857482</v>
+        <v>-6.399184680577163</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3.91</v>
       </c>
       <c r="G14" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>-16.48</v>
+        <v>-19.14</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1198,19 +1204,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>274.26</v>
+        <v>258.43</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.421063521622194</v>
+        <v>-10.88006069384095</v>
       </c>
       <c r="F15" t="n">
-        <v>1.68</v>
+        <v>3.26</v>
       </c>
       <c r="G15" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="H15" t="n">
-        <v>-20.27</v>
+        <v>-24.88</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1250,23 +1256,23 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>367.91</v>
+        <v>350.69</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.435695538057737</v>
+        <v>-7.955380577427817</v>
       </c>
       <c r="F16" t="n">
-        <v>1.94</v>
+        <v>3.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="H16" t="n">
-        <v>-17.6</v>
+        <v>-21.46</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1302,19 +1308,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>265.02</v>
+        <v>256.53</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.353356890459372</v>
+        <v>-9.353356890459374</v>
       </c>
       <c r="F17" t="n">
-        <v>2.56</v>
+        <v>5.09</v>
       </c>
       <c r="G17" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="H17" t="n">
-        <v>-22.94</v>
+        <v>-25.41</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1354,19 +1360,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>300.34</v>
+        <v>293.13</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.346734988831966</v>
+        <v>-3.715017737485216</v>
       </c>
       <c r="F18" t="n">
-        <v>3.12</v>
+        <v>5.21</v>
       </c>
       <c r="G18" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="H18" t="n">
-        <v>-19.7</v>
+        <v>-21.62</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1406,19 +1412,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1114.94</v>
+        <v>1113</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.649750707682299</v>
+        <v>-4.815660517741227</v>
       </c>
       <c r="F19" t="n">
-        <v>1.62</v>
+        <v>2.76</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.69</v>
+        <v>-6.85</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1458,19 +1464,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>534.12</v>
+        <v>542.6</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.935251798561146</v>
+        <v>-2.410071942446035</v>
       </c>
       <c r="F20" t="n">
-        <v>2.01</v>
+        <v>3.26</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.09</v>
+        <v>-0.53</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1510,19 +1516,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>249.7</v>
+        <v>244.13</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.739398612181954</v>
+        <v>-5.886661526599834</v>
       </c>
       <c r="F21" t="n">
-        <v>2.08</v>
+        <v>3.24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="H21" t="n">
-        <v>-8.029999999999999</v>
+        <v>-10.08</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1562,19 +1568,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>134.58</v>
+        <v>130.69</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.320432477102123</v>
+        <v>-9.999311342194073</v>
       </c>
       <c r="F22" t="n">
-        <v>4.38</v>
+        <v>6.28</v>
       </c>
       <c r="G22" t="n">
-        <v>1.35</v>
+        <v>0.97</v>
       </c>
       <c r="H22" t="n">
-        <v>-15.36</v>
+        <v>-17.81</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1614,19 +1620,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>216.92</v>
+        <v>210.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9071033167418641</v>
+        <v>-2.079359910685208</v>
       </c>
       <c r="F23" t="n">
-        <v>3.47</v>
+        <v>5.52</v>
       </c>
       <c r="G23" t="n">
-        <v>1.07</v>
+        <v>0.86</v>
       </c>
       <c r="H23" t="n">
-        <v>-9.039999999999999</v>
+        <v>-11.74</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1666,19 +1672,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>203.89</v>
+        <v>195.7</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.023065833733784</v>
+        <v>-5.958673714560314</v>
       </c>
       <c r="F24" t="n">
-        <v>4.84</v>
+        <v>7.62</v>
       </c>
       <c r="G24" t="n">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9399999999999999</v>
+        <v>-3.12</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1687,7 +1693,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1718,19 +1724,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>400.24</v>
+        <v>401.74</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.92549065695146</v>
+        <v>-5.572922787636614</v>
       </c>
       <c r="F25" t="n">
-        <v>2.84</v>
+        <v>4.15</v>
       </c>
       <c r="G25" t="n">
-        <v>1.33</v>
+        <v>0.98</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1770,19 +1776,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>67.33</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.235749472202677</v>
+        <v>-8.726249120337792</v>
       </c>
       <c r="F26" t="n">
-        <v>4.52</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-15.9</v>
+        <v>-19</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1822,19 +1828,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>63.58</v>
+        <v>63.02</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.06287331027978738</v>
+        <v>-0.9430996541967884</v>
       </c>
       <c r="F27" t="n">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0.85</v>
+        <v>0.66</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.56</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1874,19 +1880,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>86.43000000000001</v>
+        <v>85</v>
       </c>
       <c r="E28" t="n">
-        <v>2.042502951593872</v>
+        <v>0.3541912632821775</v>
       </c>
       <c r="F28" t="n">
-        <v>7.39</v>
+        <v>10.09</v>
       </c>
       <c r="G28" t="n">
-        <v>1.08</v>
+        <v>0.74</v>
       </c>
       <c r="H28" t="n">
-        <v>0.51</v>
+        <v>-1.15</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1903,9 +1909,9 @@
           <t>否</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>黄色加速</t>
         </is>
       </c>
     </row>
@@ -1926,19 +1932,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>38.7</v>
+        <v>38.59</v>
       </c>
       <c r="E29" t="n">
-        <v>8.922037714607377</v>
+        <v>8.612440191387559</v>
       </c>
       <c r="F29" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="G29" t="n">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="H29" t="n">
-        <v>8.460000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1955,9 +1961,9 @@
           <t>否</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>黄色加速</t>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>红色加速</t>
         </is>
       </c>
     </row>
@@ -1978,19 +1984,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>99.7</v>
+        <v>97.66</v>
       </c>
       <c r="E30" t="n">
-        <v>3.038445638693665</v>
+        <v>0.930136420008254</v>
       </c>
       <c r="F30" t="n">
-        <v>4.26</v>
+        <v>5.87</v>
       </c>
       <c r="G30" t="n">
-        <v>1.02</v>
+        <v>0.71</v>
       </c>
       <c r="H30" t="n">
-        <v>-4.13</v>
+        <v>-6.09</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2030,19 +2036,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>274</v>
+        <v>270.93</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.000831014922132</v>
+        <v>-2.110055280557854</v>
       </c>
       <c r="F31" t="n">
-        <v>1.86</v>
+        <v>2.84</v>
       </c>
       <c r="G31" t="n">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="H31" t="n">
-        <v>-7.65</v>
+        <v>-8.69</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2082,23 +2088,23 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>138.78</v>
+        <v>136.72</v>
       </c>
       <c r="E32" t="n">
-        <v>1.129490636158281</v>
+        <v>-0.3716388544778737</v>
       </c>
       <c r="F32" t="n">
-        <v>2.82</v>
+        <v>4.07</v>
       </c>
       <c r="G32" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="H32" t="n">
-        <v>1.08</v>
+        <v>-0.42</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2134,19 +2140,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>370.93</v>
+        <v>364</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.670068658378177</v>
+        <v>-3.50714418259418</v>
       </c>
       <c r="F33" t="n">
-        <v>1.19</v>
+        <v>1.84</v>
       </c>
       <c r="G33" t="n">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="H33" t="n">
-        <v>-16.19</v>
+        <v>-17.75</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2186,19 +2192,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>269.05</v>
+        <v>268.8</v>
       </c>
       <c r="E34" t="n">
-        <v>2.499142824488554</v>
+        <v>2.403901100994332</v>
       </c>
       <c r="F34" t="n">
-        <v>6.04</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="H34" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2238,19 +2244,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>40.25</v>
+        <v>40</v>
       </c>
       <c r="E35" t="n">
-        <v>2.027883396704677</v>
+        <v>1.39416983523446</v>
       </c>
       <c r="F35" t="n">
-        <v>6.11</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>1.29</v>
+        <v>0.95</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2</v>
+        <v>-0.82</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2290,19 +2296,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>309.66</v>
+        <v>300.25</v>
       </c>
       <c r="E36" t="n">
-        <v>1.727989487516446</v>
+        <v>-1.363337713534818</v>
       </c>
       <c r="F36" t="n">
-        <v>5.17</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>-26.07</v>
+        <v>-28.32</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2342,19 +2348,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>109.94</v>
+        <v>106.86</v>
       </c>
       <c r="E37" t="n">
-        <v>-4.06631762652705</v>
+        <v>-6.753926701570679</v>
       </c>
       <c r="F37" t="n">
-        <v>1.72</v>
+        <v>3.06</v>
       </c>
       <c r="G37" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="H37" t="n">
-        <v>-17.84</v>
+        <v>-20.14</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2394,19 +2400,19 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>65.47</v>
+        <v>63.3</v>
       </c>
       <c r="E38" t="n">
-        <v>-3.564589777581384</v>
+        <v>-6.76093680954486</v>
       </c>
       <c r="F38" t="n">
-        <v>4.04</v>
+        <v>6.82</v>
       </c>
       <c r="G38" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="H38" t="n">
-        <v>-18.97</v>
+        <v>-21.66</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2446,19 +2452,19 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>173.37</v>
+        <v>166.02</v>
       </c>
       <c r="E39" t="n">
-        <v>-6.017238575378103</v>
+        <v>-10.00162628069604</v>
       </c>
       <c r="F39" t="n">
-        <v>2.72</v>
+        <v>5.35</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H39" t="n">
-        <v>-16.23</v>
+        <v>-19.78</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2498,19 +2504,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>71.68000000000001</v>
+        <v>69.83</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.171928857024673</v>
+        <v>-3.722597545843098</v>
       </c>
       <c r="F40" t="n">
-        <v>2.21</v>
+        <v>3.76</v>
       </c>
       <c r="G40" t="n">
-        <v>1.11</v>
+        <v>0.95</v>
       </c>
       <c r="H40" t="n">
-        <v>-13.47</v>
+        <v>-15.7</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2550,19 +2556,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>148</v>
+        <v>146.99</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.906252050121372</v>
+        <v>-3.568851275995533</v>
       </c>
       <c r="F41" t="n">
-        <v>1.99</v>
+        <v>2.98</v>
       </c>
       <c r="G41" t="n">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="H41" t="n">
-        <v>-5.97</v>
+        <v>-6.61</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2602,19 +2608,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>349.1</v>
+        <v>342.08</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.104815864022657</v>
+        <v>-3.093484419263459</v>
       </c>
       <c r="F42" t="n">
-        <v>2.11</v>
+        <v>3.01</v>
       </c>
       <c r="G42" t="n">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.61</v>
+        <v>-2.61</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2654,19 +2660,19 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>180.29</v>
+        <v>177</v>
       </c>
       <c r="E43" t="n">
-        <v>4.195804195804187</v>
+        <v>2.294399815060966</v>
       </c>
       <c r="F43" t="n">
-        <v>9.539999999999999</v>
+        <v>13.49</v>
       </c>
       <c r="G43" t="n">
-        <v>1.92</v>
+        <v>1.37</v>
       </c>
       <c r="H43" t="n">
-        <v>-4.44</v>
+        <v>-6.18</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2683,9 +2689,9 @@
           <t>否</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>黄色加速</t>
         </is>
       </c>
     </row>
@@ -2706,19 +2712,19 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>92.93000000000001</v>
+        <v>89.55</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.962232302985545</v>
+        <v>-5.528009283679724</v>
       </c>
       <c r="F44" t="n">
-        <v>4.99</v>
+        <v>7.96</v>
       </c>
       <c r="G44" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="H44" t="n">
-        <v>-6.66</v>
+        <v>-10.05</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2758,19 +2764,19 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>129.85</v>
+        <v>127.21</v>
       </c>
       <c r="E45" t="n">
-        <v>1.923076923076916</v>
+        <v>-0.14913657770802</v>
       </c>
       <c r="F45" t="n">
-        <v>2.8</v>
+        <v>3.98</v>
       </c>
       <c r="G45" t="n">
-        <v>1.31</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>-7.04</v>
+        <v>-8.93</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2810,19 +2816,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>110.13</v>
+        <v>107</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.493738819320212</v>
+        <v>-4.293381037567078</v>
       </c>
       <c r="F46" t="n">
-        <v>3.8</v>
+        <v>5.84</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="H46" t="n">
-        <v>-8.98</v>
+        <v>-11.56</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2862,19 +2868,19 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>62.63</v>
+        <v>60.92</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.6976375455842732</v>
+        <v>-3.408910734104964</v>
       </c>
       <c r="F47" t="n">
-        <v>1.71</v>
+        <v>2.74</v>
       </c>
       <c r="G47" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="H47" t="n">
-        <v>-10.3</v>
+        <v>-12.75</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2914,19 +2920,19 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>41.48</v>
+        <v>39.46</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.008032128514059</v>
+        <v>-6.780061422159223</v>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>7.75</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H48" t="n">
-        <v>-18.14</v>
+        <v>-22.12</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2935,7 +2941,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2966,19 +2972,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.66</v>
+        <v>12.88</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.914001421464107</v>
+        <v>-8.457711442786064</v>
       </c>
       <c r="F49" t="n">
-        <v>5.89</v>
+        <v>11.75</v>
       </c>
       <c r="G49" t="n">
         <v>0.63</v>
       </c>
       <c r="H49" t="n">
-        <v>-26.95</v>
+        <v>-31.12</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2987,7 +2993,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2995,9 +3001,9 @@
           <t>否</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>黄色加速</t>
         </is>
       </c>
     </row>
@@ -3018,19 +3024,19 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>69.79000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="E50" t="n">
-        <v>-3.136710617626637</v>
+        <v>-6.689798750867448</v>
       </c>
       <c r="F50" t="n">
-        <v>3.42</v>
+        <v>6.79</v>
       </c>
       <c r="G50" t="n">
         <v>0.8</v>
       </c>
       <c r="H50" t="n">
-        <v>-13.84</v>
+        <v>-17</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3070,19 +3076,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>372.99</v>
+        <v>366.2</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.002680965147450198</v>
+        <v>-1.8230563002681</v>
       </c>
       <c r="F51" t="n">
-        <v>0.34</v>
+        <v>0.59</v>
       </c>
       <c r="G51" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.67</v>
+        <v>-2.48</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3122,19 +3128,19 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>93.73</v>
+        <v>94.14</v>
       </c>
       <c r="E52" t="n">
-        <v>2.146904969485619</v>
+        <v>2.593722755013061</v>
       </c>
       <c r="F52" t="n">
-        <v>0.92</v>
+        <v>1.74</v>
       </c>
       <c r="G52" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="H52" t="n">
-        <v>7.9</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3174,19 +3180,19 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>52.48</v>
+        <v>51.61</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3825554705432221</v>
+        <v>-1.281560826319816</v>
       </c>
       <c r="F53" t="n">
-        <v>0.92</v>
+        <v>1.62</v>
       </c>
       <c r="G53" t="n">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="H53" t="n">
-        <v>-7.75</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3226,19 +3232,19 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>46.67</v>
+        <v>49.34</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.602361374657391</v>
+        <v>4.026987138941607</v>
       </c>
       <c r="F54" t="n">
-        <v>2.04</v>
+        <v>5.75</v>
       </c>
       <c r="G54" t="n">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="H54" t="n">
-        <v>-6.27</v>
+        <v>-0.9</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3278,19 +3284,19 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>50.44</v>
+        <v>49.97</v>
       </c>
       <c r="E55" t="n">
-        <v>-2.05825242718447</v>
+        <v>-2.970873786407768</v>
       </c>
       <c r="F55" t="n">
-        <v>1.63</v>
+        <v>5.55</v>
       </c>
       <c r="G55" t="n">
-        <v>0.76</v>
+        <v>1.3</v>
       </c>
       <c r="H55" t="n">
-        <v>-9.67</v>
+        <v>-10.51</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3330,19 +3336,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>52.89</v>
+        <v>51.33</v>
       </c>
       <c r="E56" t="n">
-        <v>-3.76637554585153</v>
+        <v>-6.604803493449785</v>
       </c>
       <c r="F56" t="n">
-        <v>1.55</v>
+        <v>3.03</v>
       </c>
       <c r="G56" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H56" t="n">
-        <v>-10.85</v>
+        <v>-13.48</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3382,19 +3388,19 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>23.13</v>
+        <v>22.45</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.7722007722007707</v>
+        <v>-3.689403689403692</v>
       </c>
       <c r="F57" t="n">
-        <v>0.5</v>
+        <v>1.12</v>
       </c>
       <c r="G57" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>-9.15</v>
+        <v>-11.82</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3434,19 +3440,19 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>84.38</v>
+        <v>82.62</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.194379391100719</v>
+        <v>-3.255269320843091</v>
       </c>
       <c r="F58" t="n">
-        <v>0.58</v>
+        <v>1.03</v>
       </c>
       <c r="G58" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H58" t="n">
-        <v>-2.1</v>
+        <v>-4.14</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3486,19 +3492,19 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>109.62</v>
+        <v>105.84</v>
       </c>
       <c r="E59" t="n">
-        <v>0.6149609912803999</v>
+        <v>-2.854520422212026</v>
       </c>
       <c r="F59" t="n">
-        <v>2.22</v>
+        <v>3.94</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>-11.6</v>
+        <v>-14.65</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3538,19 +3544,19 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.98</v>
+        <v>11.86</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.1666666666666594</v>
+        <v>-1.166666666666671</v>
       </c>
       <c r="F60" t="n">
-        <v>0.67</v>
+        <v>1.24</v>
       </c>
       <c r="G60" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="H60" t="n">
-        <v>1.27</v>
+        <v>0.25</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3590,19 +3596,19 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.88</v>
+        <v>10.72</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7407407407407307</v>
+        <v>-0.7407407407407418</v>
       </c>
       <c r="F61" t="n">
-        <v>0.52</v>
+        <v>0.87</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.89</v>
+        <v>-3.34</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3642,19 +3648,19 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>7.19</v>
+        <v>7.1</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1392757660167332</v>
+        <v>-1.11420612813371</v>
       </c>
       <c r="F62" t="n">
-        <v>0.63</v>
+        <v>0.97</v>
       </c>
       <c r="G62" t="n">
-        <v>0.88</v>
+        <v>0.68</v>
       </c>
       <c r="H62" t="n">
-        <v>-4.13</v>
+        <v>-5.33</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3694,19 +3700,19 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>61.77</v>
+        <v>61.09</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4833252779120278</v>
+        <v>-1.578862574512641</v>
       </c>
       <c r="F63" t="n">
-        <v>1.68</v>
+        <v>2.77</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="H63" t="n">
-        <v>-6.42</v>
+        <v>-7.45</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3746,19 +3752,19 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>70.48999999999999</v>
+        <v>68.45</v>
       </c>
       <c r="E64" t="n">
-        <v>-2.516940948693136</v>
+        <v>-5.338127506568934</v>
       </c>
       <c r="F64" t="n">
-        <v>0.96</v>
+        <v>2.06</v>
       </c>
       <c r="G64" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="H64" t="n">
-        <v>-12.52</v>
+        <v>-15.05</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3798,19 +3804,19 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>29.46</v>
+        <v>29.25</v>
       </c>
       <c r="E65" t="n">
-        <v>2.185223725286178</v>
+        <v>1.456815816857437</v>
       </c>
       <c r="F65" t="n">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="G65" t="n">
-        <v>1.24</v>
+        <v>0.96</v>
       </c>
       <c r="H65" t="n">
-        <v>6.66</v>
+        <v>5.9</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3850,23 +3856,23 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>18.41</v>
+        <v>18.2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.791736460078176</v>
+        <v>1.619207146845336</v>
       </c>
       <c r="F66" t="n">
-        <v>0.95</v>
+        <v>1.47</v>
       </c>
       <c r="G66" t="n">
-        <v>1.25</v>
+        <v>0.97</v>
       </c>
       <c r="H66" t="n">
-        <v>7.1</v>
+        <v>5.88</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3902,19 +3908,19 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>39.31</v>
+        <v>38.87</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.6319514661274006</v>
+        <v>-1.744186046511642</v>
       </c>
       <c r="F67" t="n">
-        <v>0.68</v>
+        <v>1.26</v>
       </c>
       <c r="G67" t="n">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="H67" t="n">
-        <v>-8.539999999999999</v>
+        <v>-9.56</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3954,19 +3960,19 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>42.81</v>
+        <v>43.27</v>
       </c>
       <c r="E68" t="n">
-        <v>-2.014190890363921</v>
+        <v>-0.9613183794918601</v>
       </c>
       <c r="F68" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="G68" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="H68" t="n">
-        <v>4.16</v>
+        <v>5.28</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4006,19 +4012,19 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>24.86</v>
+        <v>24.68</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.622477245745946</v>
+        <v>-2.334784329244166</v>
       </c>
       <c r="F69" t="n">
-        <v>0.63</v>
+        <v>1.3</v>
       </c>
       <c r="G69" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="H69" t="n">
-        <v>-4.71</v>
+        <v>-5.4</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4058,19 +4064,19 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>8.84</v>
+        <v>8.68</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.559020044543435</v>
+        <v>-3.340757238307357</v>
       </c>
       <c r="F70" t="n">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="G70" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="H70" t="n">
-        <v>9.140000000000001</v>
+        <v>7.16</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4110,19 +4116,19 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>68.23</v>
+        <v>65.5</v>
       </c>
       <c r="E71" t="n">
-        <v>-2.764714265355561</v>
+        <v>-6.655265783098196</v>
       </c>
       <c r="F71" t="n">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="G71" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="H71" t="n">
-        <v>-26.4</v>
+        <v>-29.34</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4162,19 +4168,19 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>37.64</v>
+        <v>36.22</v>
       </c>
       <c r="E72" t="n">
-        <v>-2.411200414830184</v>
+        <v>-6.092818252527876</v>
       </c>
       <c r="F72" t="n">
-        <v>3.21</v>
+        <v>5.68</v>
       </c>
       <c r="G72" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="H72" t="n">
-        <v>-22.23</v>
+        <v>-25.17</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4183,7 +4189,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4214,19 +4220,19 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>102.08</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>-2.511698978130072</v>
+        <v>-6.475026263012118</v>
       </c>
       <c r="F73" t="n">
-        <v>1.96</v>
+        <v>3.94</v>
       </c>
       <c r="G73" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="H73" t="n">
-        <v>-23.48</v>
+        <v>-26.59</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4266,19 +4272,19 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>105.2</v>
+        <v>101.7</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.3410382720727578</v>
+        <v>-3.656688139446762</v>
       </c>
       <c r="F74" t="n">
-        <v>2.28</v>
+        <v>3.51</v>
       </c>
       <c r="G74" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="H74" t="n">
-        <v>-23</v>
+        <v>-25.56</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4287,7 +4293,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4318,19 +4324,19 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>62.49</v>
+        <v>59.11</v>
       </c>
       <c r="E75" t="n">
-        <v>-3.535041679530715</v>
+        <v>-8.752701451065148</v>
       </c>
       <c r="F75" t="n">
-        <v>2.65</v>
+        <v>5.33</v>
       </c>
       <c r="G75" t="n">
         <v>0.77</v>
       </c>
       <c r="H75" t="n">
-        <v>-21.48</v>
+        <v>-25.72</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4339,7 +4345,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4370,19 +4376,19 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>31.45</v>
+        <v>30.07</v>
       </c>
       <c r="E76" t="n">
-        <v>-3.734312825221919</v>
+        <v>-7.958371594735237</v>
       </c>
       <c r="F76" t="n">
-        <v>1.9</v>
+        <v>4.17</v>
       </c>
       <c r="G76" t="n">
-        <v>0.74</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>-21.34</v>
+        <v>-24.79</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4422,19 +4428,19 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>77.81999999999999</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="E77" t="n">
-        <v>-3.305168986083518</v>
+        <v>-8.039264413518888</v>
       </c>
       <c r="F77" t="n">
-        <v>3.31</v>
+        <v>6.03</v>
       </c>
       <c r="G77" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H77" t="n">
-        <v>-19.02</v>
+        <v>-22.99</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4474,19 +4480,19 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>125.01</v>
+        <v>120.24</v>
       </c>
       <c r="E78" t="n">
-        <v>-3.712547177077719</v>
+        <v>-7.386582453978296</v>
       </c>
       <c r="F78" t="n">
-        <v>1.36</v>
+        <v>2.52</v>
       </c>
       <c r="G78" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="H78" t="n">
-        <v>-20.21</v>
+        <v>-23.25</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4526,19 +4532,19 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>48.24</v>
+        <v>47.6</v>
       </c>
       <c r="E79" t="n">
-        <v>1.557894736842114</v>
+        <v>0.2105263157894832</v>
       </c>
       <c r="F79" t="n">
-        <v>0.61</v>
+        <v>0.98</v>
       </c>
       <c r="G79" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H79" t="n">
-        <v>-11.95</v>
+        <v>-13.12</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4578,19 +4584,19 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.07</v>
+        <v>12.88</v>
       </c>
       <c r="E80" t="n">
-        <v>-8.665269042627532</v>
+        <v>-9.993011879804325</v>
       </c>
       <c r="F80" t="n">
-        <v>11.96</v>
+        <v>13.58</v>
       </c>
       <c r="G80" t="n">
-        <v>1.06</v>
+        <v>0.6</v>
       </c>
       <c r="H80" t="n">
-        <v>-18.26</v>
+        <v>-19.45</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4630,19 +4636,19 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>29</v>
+        <v>27.62</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.590425531914887</v>
+        <v>-8.178191489361698</v>
       </c>
       <c r="F81" t="n">
-        <v>2.94</v>
+        <v>5.89</v>
       </c>
       <c r="G81" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="H81" t="n">
-        <v>-20.72</v>
+        <v>-24.49</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4682,19 +4688,19 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>20.35</v>
+        <v>19.99</v>
       </c>
       <c r="E82" t="n">
-        <v>2.467270896273921</v>
+        <v>0.654582074521648</v>
       </c>
       <c r="F82" t="n">
-        <v>4.27</v>
+        <v>6.25</v>
       </c>
       <c r="G82" t="n">
-        <v>1.08</v>
+        <v>0.79</v>
       </c>
       <c r="H82" t="n">
-        <v>0.89</v>
+        <v>-0.89</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4734,19 +4740,19 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>57.56</v>
+        <v>56.97</v>
       </c>
       <c r="E83" t="n">
-        <v>1.035632789187302</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>1.3</v>
+        <v>2.17</v>
       </c>
       <c r="G83" t="n">
-        <v>0.93</v>
+        <v>0.78</v>
       </c>
       <c r="H83" t="n">
-        <v>-2.46</v>
+        <v>-3.46</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4780,15 +4786,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.600000000000001" customWidth="1" min="1" max="1"/>
     <col width="25.6" customWidth="1" min="2" max="2"/>
     <col width="9.600000000000001" customWidth="1" min="3" max="3"/>
     <col width="12.8" customWidth="1" min="4" max="4"/>
-    <col width="14.4" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="20.8" customWidth="1" min="5" max="5"/>
+    <col width="33.6" customWidth="1" min="6" max="6"/>
     <col width="41.6" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4837,27 +4843,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AI服务器/PCB/算力基建</t>
+          <t>芯片设计/IDM/制造</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>紫光股份</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>000938</t>
+          <t>688008</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>换手11.8%</t>
+          <t>换手10.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DIF&gt;DEA多头；偏卖点</t>
+          <t>DIF&lt;DEA空头；偏买点</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4874,30 +4880,178 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>AI服务器/PCB/算力基建</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>浪潮信息</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>000977</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>换手10.1%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DIF&gt;DEA多头；多空信号并存，观望</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>趋势加速中，持仓可持有但设移动止盈，空仓不重仓追</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>红色加速</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AI服务器/PCB/算力基建</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>紫光股份</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>000938</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>换手15.8%&gt;15%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DIF&gt;DEA多头；偏卖点</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>过热风险大，不追高，持仓考虑分批兑现</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>黄色加速</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PCB上游先进材料</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>华正新材</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>603186</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>换手13.5%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DIF&lt;DEA空头；偏买点</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>趋势加速中，持仓可持有但设移动止盈，空仓不重仓追</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>黄色加速</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PCB上游先进材料</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>黄河旋风</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>600172</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>换手11.8%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DIF&lt;DEA空头；无明确信号</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>趋势加速中，持仓可持有但设移动止盈，空仓不重仓追</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>黄色加速</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>功率半导体/功率器件</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>华微电子</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>600360</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>换手12.0%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>换手13.6%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>死叉(零轴上方)；偏卖点</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>趋势加速中，持仓可持有但设移动止盈，空仓不重仓追</t>
         </is>
@@ -4914,22 +5068,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.600000000000001" customWidth="1" min="1" max="1"/>
     <col width="12.8" customWidth="1" min="2" max="2"/>
     <col width="17.6" customWidth="1" min="3" max="3"/>
-    <col width="11.2" customWidth="1" min="4" max="4"/>
+    <col width="12.8" customWidth="1" min="4" max="4"/>
     <col width="11.2" customWidth="1" min="5" max="5"/>
     <col width="9.600000000000001" customWidth="1" min="6" max="6"/>
     <col width="9.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="9.600000000000001" customWidth="1" min="8" max="8"/>
+    <col width="11.2" customWidth="1" min="8" max="8"/>
     <col width="9.600000000000001" customWidth="1" min="9" max="9"/>
-    <col width="9.600000000000001" customWidth="1" min="10" max="10"/>
+    <col width="19.2" customWidth="1" min="10" max="10"/>
     <col width="35.2" customWidth="1" min="11" max="11"/>
     <col width="11.2" customWidth="1" min="12" max="12"/>
-    <col width="11.2" customWidth="1" min="13" max="13"/>
+    <col width="17.6" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5002,45 +5156,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>紫光股份</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>000938</t>
+          <t>688008</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DIF&gt;DEA多头</t>
+          <t>DIF&lt;DEA空头</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.563</v>
+        <v>-1.132</v>
       </c>
       <c r="E2" t="n">
-        <v>1.73</v>
+        <v>5.555</v>
       </c>
       <c r="F2" t="n">
-        <v>77.40000000000001</v>
+        <v>22.3</v>
       </c>
       <c r="G2" t="n">
-        <v>79.5</v>
+        <v>28.1</v>
       </c>
       <c r="H2" t="n">
-        <v>73.2</v>
+        <v>10.7</v>
       </c>
       <c r="I2" t="n">
-        <v>67.7</v>
+        <v>39.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>KDJ超卖金叉</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>KDJ超买死叉</t>
+          <t>无</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -5050,60 +5204,280 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>偏卖点</t>
+          <t>偏买点</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>浪潮信息</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000977</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DIF&gt;DEA多头</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.517</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.779</v>
+      </c>
+      <c r="F3" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="I3" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MACD底背离(强)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>KDJ超买死叉</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>多空信号并存，观望</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>紫光股份</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000938</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DIF&gt;DEA多头</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="F4" t="n">
+        <v>77</v>
+      </c>
+      <c r="G4" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>KDJ超买死叉</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>偏卖点</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>华正新材</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>603186</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DIF&lt;DEA空头</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8.432</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>KDJ超卖金叉</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>偏买点</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>黄河旋风</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>600172</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DIF&lt;DEA空头</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>无明确信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>华微电子</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>600360</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>死叉(零轴上方)</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="F3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="I3" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="D7" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="F7" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>MACD死叉(零轴上方)、KDJ超买死叉</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>强卖点共振</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>偏卖点</t>
         </is>
@@ -5170,10 +5544,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.87</v>
+        <v>0.54</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
@@ -5185,7 +5559,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>紫光股份(+8.9%)、中科曙光(+3.0%)、东山精密(+2.5%)</t>
+          <t>紫光股份(+8.6%)、东山精密(+2.4%)、中兴通讯(+1.4%)</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5570,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.14</v>
+        <v>-0.88</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -5211,24 +5585,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>洛阳钼业(+2.8%)、紫金矿业(+2.2%)、北方稀土(-0.6%)</t>
+          <t>洛阳钼业(+1.6%)、紫金矿业(+1.5%)、中国神华(-1.0%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>新能源-光伏/储能</t>
+          <t>新能源-电池/锂矿</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.28</v>
+        <v>-1.63</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -5237,24 +5611,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>通威股份(+0.7%)、阳光电源(+0.6%)、晶澳科技(+0.1%)</t>
+          <t>天齐锂业(+4.0%)、比亚迪(+2.6%)、亿纬锂能(-1.3%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>新能源-电池/锂矿</t>
+          <t>新能源-光伏/储能</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.86</v>
+        <v>-2.13</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -5263,7 +5637,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>比亚迪(+2.1%)、亿纬锂能(+0.4%)、宁德时代(-0.0%)</t>
+          <t>通威股份(-0.7%)、晶澳科技(-1.1%)、隆基绿能(-1.2%)</t>
         </is>
       </c>
     </row>
@@ -5274,10 +5648,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.1</v>
+        <v>-4.74</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -5289,7 +5663,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>海光信息(+2.6%)、华虹公司(+2.6%)、中芯国际(+1.9%)</t>
+          <t>华虹公司(-1.1%)、韦尔股份(-1.1%)、海光信息(-1.1%)</t>
         </is>
       </c>
     </row>
@@ -5300,10 +5674,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.78</v>
+        <v>-4.78</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
@@ -5315,24 +5689,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>华正新材(+4.2%)、铜冠铜箔(+1.9%)、隆扬电子(-0.7%)</t>
+          <t>华正新材(+2.3%)、铜冠铜箔(-0.1%)、南亚新材(-3.1%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>功率半导体/功率器件</t>
+          <t>光通信/CPO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3</v>
+        <v>-5.68</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -5341,24 +5715,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>时代电气(+1.6%)、扬杰科技(-0.3%)、士兰微(-2.4%)</t>
+          <t>光迅科技(-2.1%)、新易盛(-2.4%)、中际旭创(-4.8%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>半导体设备/材料</t>
+          <t>功率半导体/功率器件</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-3.95</v>
+        <v>-6.63</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -5367,21 +5741,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>长川科技(-1.3%)、北方华创(-3.0%)、芯源微(-3.3%)</t>
+          <t>时代电气(+0.2%)、扬杰科技(-3.7%)、士兰微(-6.1%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>光通信/CPO</t>
+          <t>半导体设备/材料</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-3.99</v>
+        <v>-7.25</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -5393,7 +5767,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>光迅科技(+0.9%)、剑桥科技(-2.0%)、天孚通信(-3.7%)</t>
+          <t>长川科技(-3.7%)、北方华创(-5.4%)、芯源微(-6.4%)</t>
         </is>
       </c>
     </row>
